--- a/manufacturing_forms/015_manufacturing_line_shutdown_notice_request_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/015_manufacturing_line_shutdown_notice_request_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1094,34 +1094,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>manager_signature_choices</t>
+          <t>approver_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jane_doe</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jane Doe</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>manager_signature_choices</t>
+          <t>approver_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>john_doe</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1133,112 +1133,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>manager_note_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>manager_note_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>joe</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Joe</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>approver_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>jane</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>approver_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>john</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>manager_note_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>manager_note_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>False</t>
         </is>
